--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123965797</v>
+        <v>123965535</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>5361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588902</v>
+        <v>589005</v>
       </c>
       <c r="R2" t="n">
-        <v>6343736</v>
+        <v>6343662</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965980</v>
+        <v>123967098</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,29 +815,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589003</v>
+        <v>588544</v>
       </c>
       <c r="R3" t="n">
-        <v>6343705</v>
+        <v>6343791</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123966973</v>
+        <v>123967372</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,28 +900,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -933,17 +925,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588741</v>
+        <v>588492</v>
       </c>
       <c r="R4" t="n">
-        <v>6343930</v>
+        <v>6343902</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965535</v>
+        <v>123965980</v>
       </c>
       <c r="B5" t="n">
-        <v>5361</v>
+        <v>58136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,38 +1003,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589005</v>
+        <v>589003</v>
       </c>
       <c r="R5" t="n">
-        <v>6343662</v>
+        <v>6343705</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1077,11 +1078,6 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1094,22 +1090,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967098</v>
+        <v>123965797</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,20 +1114,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1142,14 +1138,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588544</v>
+        <v>588902</v>
       </c>
       <c r="R6" t="n">
-        <v>6343791</v>
+        <v>6343736</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967372</v>
+        <v>123966973</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,24 +1220,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588492</v>
+        <v>588741</v>
       </c>
       <c r="R7" t="n">
-        <v>6343902</v>
+        <v>6343930</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967098</v>
+        <v>123965980</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,20 +815,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588544</v>
+        <v>589003</v>
       </c>
       <c r="R3" t="n">
-        <v>6343791</v>
+        <v>6343705</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967372</v>
+        <v>123965797</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588492</v>
+        <v>588902</v>
       </c>
       <c r="R4" t="n">
-        <v>6343902</v>
+        <v>6343736</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965980</v>
+        <v>123966973</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,20 +1007,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1026,7 +1030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589003</v>
+        <v>588741</v>
       </c>
       <c r="R5" t="n">
-        <v>6343705</v>
+        <v>6343930</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1102,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123965797</v>
+        <v>123967098</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,20 +1118,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,14 +1142,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588902</v>
+        <v>588544</v>
       </c>
       <c r="R6" t="n">
-        <v>6343736</v>
+        <v>6343791</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123966973</v>
+        <v>123967372</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>58349</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,28 +1224,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588741</v>
+        <v>588492</v>
       </c>
       <c r="R7" t="n">
-        <v>6343930</v>
+        <v>6343902</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123965535</v>
+        <v>123965797</v>
       </c>
       <c r="B2" t="n">
-        <v>5361</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589005</v>
+        <v>588902</v>
       </c>
       <c r="R2" t="n">
-        <v>6343662</v>
+        <v>6343736</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965980</v>
+        <v>123967372</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,32 +789,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -827,17 +818,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589003</v>
+        <v>588492</v>
       </c>
       <c r="R3" t="n">
-        <v>6343705</v>
+        <v>6343902</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965797</v>
+        <v>123965535</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>5361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588902</v>
+        <v>589005</v>
       </c>
       <c r="R4" t="n">
-        <v>6343736</v>
+        <v>6343662</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123966973</v>
+        <v>123967098</v>
       </c>
       <c r="B5" t="n">
         <v>57861</v>
@@ -1028,29 +1024,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588741</v>
+        <v>588544</v>
       </c>
       <c r="R5" t="n">
-        <v>6343930</v>
+        <v>6343791</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967098</v>
+        <v>123965980</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>58136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,20 +1105,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,20 +1126,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588544</v>
+        <v>589003</v>
       </c>
       <c r="R6" t="n">
-        <v>6343791</v>
+        <v>6343705</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967372</v>
+        <v>123966973</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,24 +1220,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588492</v>
+        <v>588741</v>
       </c>
       <c r="R7" t="n">
-        <v>6343902</v>
+        <v>6343930</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123965797</v>
+        <v>123966973</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588902</v>
+        <v>588741</v>
       </c>
       <c r="R2" t="n">
-        <v>6343736</v>
+        <v>6343930</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967372</v>
+        <v>123965797</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588492</v>
+        <v>588902</v>
       </c>
       <c r="R3" t="n">
-        <v>6343902</v>
+        <v>6343736</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965535</v>
+        <v>123967098</v>
       </c>
       <c r="B4" t="n">
-        <v>5361</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589005</v>
+        <v>588544</v>
       </c>
       <c r="R4" t="n">
-        <v>6343662</v>
+        <v>6343791</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967098</v>
+        <v>123965980</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>58136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,20 +1002,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,20 +1023,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588544</v>
+        <v>589003</v>
       </c>
       <c r="R5" t="n">
-        <v>6343791</v>
+        <v>6343705</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123965980</v>
+        <v>123967372</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,32 +1113,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1138,17 +1142,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589003</v>
+        <v>588492</v>
       </c>
       <c r="R6" t="n">
-        <v>6343705</v>
+        <v>6343902</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123966973</v>
+        <v>123965535</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>5361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,47 +1220,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>101728</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588741</v>
+        <v>589005</v>
       </c>
       <c r="R7" t="n">
-        <v>6343930</v>
+        <v>6343662</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1291,6 +1286,11 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965980</v>
+        <v>123965797</v>
       </c>
       <c r="B3" t="n">
-        <v>58158</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,29 +819,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589003</v>
+        <v>588902</v>
       </c>
       <c r="R3" t="n">
-        <v>6343705</v>
+        <v>6343736</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,12 +876,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1106,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123965797</v>
+        <v>123967372</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>58371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,38 +1109,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588902</v>
+        <v>588492</v>
       </c>
       <c r="R6" t="n">
-        <v>6343736</v>
+        <v>6343902</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967372</v>
+        <v>123965980</v>
       </c>
       <c r="B7" t="n">
-        <v>58371</v>
+        <v>58158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,28 +1216,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588492</v>
+        <v>589003</v>
       </c>
       <c r="R7" t="n">
-        <v>6343902</v>
+        <v>6343705</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123966973</v>
+        <v>123967098</v>
       </c>
       <c r="B2" t="n">
         <v>57883</v>
@@ -708,29 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588741</v>
+        <v>588544</v>
       </c>
       <c r="R2" t="n">
-        <v>6343930</v>
+        <v>6343791</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965797</v>
+        <v>123967372</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>58371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588902</v>
+        <v>588492</v>
       </c>
       <c r="R3" t="n">
-        <v>6343736</v>
+        <v>6343902</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967098</v>
+        <v>123965797</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588544</v>
+        <v>588902</v>
       </c>
       <c r="R4" t="n">
-        <v>6343791</v>
+        <v>6343736</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965535</v>
+        <v>123965980</v>
       </c>
       <c r="B5" t="n">
-        <v>5361</v>
+        <v>58158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589005</v>
+        <v>589003</v>
       </c>
       <c r="R5" t="n">
-        <v>6343662</v>
+        <v>6343705</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1068,11 +1073,6 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1085,22 +1085,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967372</v>
+        <v>123965535</v>
       </c>
       <c r="B6" t="n">
-        <v>58371</v>
+        <v>5361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,46 +1109,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>101728</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588492</v>
+        <v>589005</v>
       </c>
       <c r="R6" t="n">
-        <v>6343902</v>
+        <v>6343662</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123965980</v>
+        <v>123966973</v>
       </c>
       <c r="B7" t="n">
-        <v>58158</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,20 +1216,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589003</v>
+        <v>588741</v>
       </c>
       <c r="R7" t="n">
-        <v>6343705</v>
+        <v>6343930</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123967098</v>
+        <v>123965535</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>5361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>101728</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588544</v>
+        <v>589005</v>
       </c>
       <c r="R2" t="n">
-        <v>6343791</v>
+        <v>6343662</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965797</v>
+        <v>123967098</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588902</v>
+        <v>588544</v>
       </c>
       <c r="R4" t="n">
-        <v>6343736</v>
+        <v>6343791</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965980</v>
+        <v>123965797</v>
       </c>
       <c r="B5" t="n">
-        <v>58158</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,20 +1003,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1019,29 +1024,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589003</v>
+        <v>588902</v>
       </c>
       <c r="R5" t="n">
-        <v>6343705</v>
+        <v>6343736</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123965535</v>
+        <v>123966973</v>
       </c>
       <c r="B6" t="n">
-        <v>5361</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,38 +1105,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101728</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589005</v>
+        <v>588741</v>
       </c>
       <c r="R6" t="n">
-        <v>6343662</v>
+        <v>6343930</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1175,11 +1180,6 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1192,22 +1192,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123966973</v>
+        <v>123965980</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>58158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,20 +1216,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588741</v>
+        <v>589003</v>
       </c>
       <c r="R7" t="n">
-        <v>6343930</v>
+        <v>6343705</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123965535</v>
+        <v>123966973</v>
       </c>
       <c r="B2" t="n">
-        <v>5361</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101728</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589005</v>
+        <v>588741</v>
       </c>
       <c r="R2" t="n">
-        <v>6343662</v>
+        <v>6343930</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -753,11 +762,6 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967372</v>
+        <v>123965797</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588492</v>
+        <v>588902</v>
       </c>
       <c r="R3" t="n">
-        <v>6343902</v>
+        <v>6343736</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967098</v>
+        <v>123965980</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>58158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +900,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,20 +921,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588544</v>
+        <v>589003</v>
       </c>
       <c r="R4" t="n">
-        <v>6343791</v>
+        <v>6343705</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965797</v>
+        <v>123965535</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588902</v>
+        <v>589005</v>
       </c>
       <c r="R5" t="n">
-        <v>6343736</v>
+        <v>6343662</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123966973</v>
+        <v>123967098</v>
       </c>
       <c r="B6" t="n">
         <v>57883</v>
@@ -1126,29 +1139,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588741</v>
+        <v>588544</v>
       </c>
       <c r="R6" t="n">
-        <v>6343930</v>
+        <v>6343791</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123965980</v>
+        <v>123967372</v>
       </c>
       <c r="B7" t="n">
-        <v>58158</v>
+        <v>58371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,32 +1220,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589003</v>
+        <v>588492</v>
       </c>
       <c r="R7" t="n">
-        <v>6343705</v>
+        <v>6343902</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 12388-2025 artfynd.xlsx
+++ b/artfynd/A 12388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123966973</v>
+        <v>123965535</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>5361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>101728</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog vid Överby, Skog vid Överby, Sm</t>
+          <t>Flundreberget, Flundreberget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588741</v>
+        <v>589005</v>
       </c>
       <c r="R2" t="n">
-        <v>6343930</v>
+        <v>6343662</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -762,6 +753,11 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kläckhål i stående asp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965980</v>
+        <v>123966973</v>
       </c>
       <c r="B4" t="n">
-        <v>58158</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589003</v>
+        <v>588741</v>
       </c>
       <c r="R4" t="n">
-        <v>6343705</v>
+        <v>6343930</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965535</v>
+        <v>123967098</v>
       </c>
       <c r="B5" t="n">
-        <v>5361</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,41 +1007,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flundreberget, Flundreberget, Sm</t>
+          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589005</v>
+        <v>588544</v>
       </c>
       <c r="R5" t="n">
-        <v>6343662</v>
+        <v>6343791</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål i stående asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967098</v>
+        <v>123967372</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>58371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,34 +1113,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588544</v>
+        <v>588492</v>
       </c>
       <c r="R6" t="n">
-        <v>6343791</v>
+        <v>6343902</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967372</v>
+        <v>123965980</v>
       </c>
       <c r="B7" t="n">
-        <v>58371</v>
+        <v>58158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,28 +1216,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Borgäng, Lilla Borgäng, Sm</t>
+          <t>Skog vid Överby, Skog vid Överby, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588492</v>
+        <v>589003</v>
       </c>
       <c r="R7" t="n">
-        <v>6343902</v>
+        <v>6343705</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
